--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,12 +35,8 @@
       <b val="1"/>
       <color rgb="00385723"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,14 +82,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,11 +532,11 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0445</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -584,11 +573,11 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0286</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -625,11 +614,11 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0302</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -666,11 +655,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0166</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -707,11 +696,11 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0402</v>
+        <v>0.0272</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -748,11 +737,11 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.0348</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -789,11 +778,11 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.036</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -830,11 +819,11 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0358</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -871,11 +860,11 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.0359</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -912,11 +901,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0111</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -953,11 +942,11 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0381</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -994,11 +983,11 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0275</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1035,11 +1024,11 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.04</v>
+        <v>0.0362</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1076,11 +1065,11 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0157</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1117,11 +1106,11 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0266</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1158,11 +1147,11 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0147</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1199,11 +1188,11 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0321</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1240,11 +1229,11 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0071</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1281,11 +1270,11 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0425</v>
+        <v>0.0317</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1322,11 +1311,11 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0316</v>
+        <v>0.0317</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1363,11 +1352,11 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0109</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1404,11 +1393,11 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0067</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1445,11 +1434,11 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0063</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1486,11 +1475,11 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0312</v>
+        <v>0.0395</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1527,11 +1516,11 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0412</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1568,11 +1557,11 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0223</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1609,11 +1598,11 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.0332</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1650,11 +1639,11 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.019</v>
+        <v>0.0226</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1691,11 +1680,11 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0104</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1732,11 +1721,11 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0159</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1773,11 +1762,11 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0429</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1814,11 +1803,11 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0344</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1855,11 +1844,11 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0386</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1896,11 +1885,11 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.024</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1937,11 +1926,11 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0286</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1978,11 +1967,11 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0303</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2019,11 +2008,11 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0202</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2060,11 +2049,11 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.012</v>
+        <v>0.0431</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2101,11 +2090,11 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0136</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2142,11 +2131,11 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0381</v>
+        <v>0.0386</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2183,11 +2172,11 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0415</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2224,11 +2213,11 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0382</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2265,11 +2254,11 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0371</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,24 +2293,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0159</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected valid return type, received mismatched value.</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2351,11 +2336,11 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.0221</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2392,11 +2377,11 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0421</v>
+        <v>0.0307</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2433,11 +2418,11 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0131</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2474,11 +2459,11 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0355</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2515,11 +2500,11 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0229</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2556,11 +2541,11 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2597,11 +2582,11 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.031</v>
+        <v>0.0424</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2638,11 +2623,11 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0055</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2679,11 +2664,11 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0316</v>
+        <v>0.0315</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2720,11 +2705,11 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0309</v>
+        <v>0.0206</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2761,11 +2746,11 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0437</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2802,11 +2787,11 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0379</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2843,11 +2828,11 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2884,11 +2869,11 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0095</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2925,11 +2910,11 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.011</v>
+        <v>0.0126</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2966,11 +2951,11 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0121</v>
+        <v>0.0116</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3007,11 +2992,11 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.0424</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3048,11 +3033,11 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0389</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3089,11 +3074,11 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.028</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3130,11 +3115,11 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0175</v>
+        <v>0.0094</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3171,11 +3156,11 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0053</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3212,11 +3197,11 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0164</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3253,11 +3238,11 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0091</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3294,11 +3279,11 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0298</v>
+        <v>0.0388</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3335,11 +3320,11 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.029</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3376,11 +3361,11 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0125</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3417,11 +3402,11 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.0179</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3458,11 +3443,11 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.0291</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3499,11 +3484,11 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0065</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3540,11 +3525,11 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.0073</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3581,11 +3566,11 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0177</v>
+        <v>0.0331</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3622,11 +3607,11 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.0408</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3663,11 +3648,11 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.0182</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3704,11 +3689,11 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0316</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3745,11 +3730,11 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0142</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3786,11 +3771,11 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0136</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3827,11 +3812,11 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0277</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3868,11 +3853,11 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0364</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3909,11 +3894,11 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.0315</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3950,11 +3935,11 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0182</v>
+        <v>0.0409</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3991,11 +3976,11 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0417</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4032,11 +4017,11 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.0401</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4073,11 +4058,11 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0166</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4114,11 +4099,11 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0058</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4153,24 +4138,20 @@
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0232</v>
+        <v>0.0416</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected valid return type, received mismatched value.</t>
-        </is>
-      </c>
+      <c r="I90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4200,11 +4181,11 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0197</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4241,11 +4222,11 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0186</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4282,11 +4263,11 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0146</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4323,11 +4304,11 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0331</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4364,11 +4345,11 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0112</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4405,11 +4386,11 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0419</v>
+        <v>0.0309</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4446,11 +4427,11 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.0167</v>
+        <v>0.034</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4487,11 +4468,11 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0139</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4528,11 +4509,11 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0147</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4569,11 +4550,11 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0129</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4610,11 +4591,11 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0267</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4651,11 +4632,11 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0069</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4692,11 +4673,11 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0297</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4733,11 +4714,11 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0103</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4774,11 +4755,11 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0236</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4815,11 +4796,11 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0098</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4856,11 +4837,11 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0376</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4897,11 +4878,11 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.0173</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4938,11 +4919,11 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0097</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4979,11 +4960,11 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5020,11 +5001,11 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0397</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5061,11 +5042,11 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0244</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5102,11 +5083,11 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0351</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5143,11 +5124,11 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0062</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5184,11 +5165,11 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0243</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5225,11 +5206,11 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0147</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5266,11 +5247,11 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.0059</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5307,11 +5288,11 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0271</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5348,11 +5329,11 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0412</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5389,11 +5370,11 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0383</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5430,11 +5411,11 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0139</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5471,11 +5452,11 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0322</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5512,11 +5493,11 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0413</v>
+        <v>0.0261</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5553,11 +5534,11 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0118</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5594,11 +5575,11 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0263</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5635,11 +5616,11 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0365</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5676,11 +5657,11 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0144</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5717,11 +5698,11 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0137</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5758,11 +5739,11 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0312</v>
+        <v>0.0089</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5799,11 +5780,11 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0229</v>
+        <v>0.0372</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5840,11 +5821,11 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0382</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5881,11 +5862,11 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0126</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5922,11 +5903,11 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0072</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5963,11 +5944,11 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0092</v>
+        <v>0.0331</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -6002,24 +5983,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.0074</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected valid return type, received mismatched value.</t>
-        </is>
-      </c>
+      <c r="I135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6049,11 +6026,11 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0396</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6090,11 +6067,11 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0383</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6131,11 +6108,11 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0195</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6172,11 +6149,11 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0336</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6213,11 +6190,11 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0419</v>
+        <v>0.0055</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6254,11 +6231,11 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0411</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6295,11 +6272,11 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0191</v>
+        <v>0.0198</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6336,11 +6313,11 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0322</v>
+        <v>0.0249</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6377,11 +6354,11 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0346</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6418,11 +6395,11 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0135</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6459,11 +6436,11 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0123</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6500,11 +6477,11 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0271</v>
+        <v>0.0413</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6541,11 +6518,11 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.03</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6582,11 +6559,11 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0414</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6623,11 +6600,11 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0409</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6664,11 +6641,11 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0191</v>
+        <v>0.0182</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6705,11 +6682,11 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.025</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6746,11 +6723,11 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.0113</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6787,11 +6764,11 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0446</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6828,11 +6805,11 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0237</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6869,11 +6846,11 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0288</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6910,11 +6887,11 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6951,11 +6928,11 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0392</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6992,11 +6969,11 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0059</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7033,11 +7010,11 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0253</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7074,11 +7051,11 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0134</v>
+        <v>0.0246</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7115,11 +7092,11 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0144</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7156,11 +7133,11 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0094</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7197,11 +7174,11 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0229</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7238,11 +7215,11 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0417</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7279,11 +7256,11 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0242</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7320,11 +7297,11 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0327</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7361,11 +7338,11 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0115</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7402,11 +7379,11 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0245</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7443,11 +7420,11 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0184</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7484,11 +7461,11 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.0355</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7525,11 +7502,11 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0412</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7566,11 +7543,11 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0237</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7607,11 +7584,11 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0263</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7648,11 +7625,11 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0442</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7689,11 +7666,11 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0399</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7730,11 +7707,11 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0148</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7771,11 +7748,11 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0171</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7812,11 +7789,11 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0159</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7851,24 +7828,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0356</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected valid return type, received mismatched value.</t>
-        </is>
-      </c>
+      <c r="I180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -7898,11 +7871,11 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7939,11 +7912,11 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.03</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7980,11 +7953,11 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0238</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8021,11 +7994,11 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0377</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8062,11 +8035,11 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.037</v>
+        <v>0.011</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8103,11 +8076,11 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.013</v>
+        <v>0.0181</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8144,11 +8117,11 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0227</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8185,11 +8158,11 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0264</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8226,11 +8199,11 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.013</v>
+        <v>0.0219</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8267,11 +8240,11 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.044</v>
+        <v>0.0119</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8308,11 +8281,11 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0207</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8349,11 +8322,11 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0262</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8390,11 +8363,11 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0199</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8431,11 +8404,11 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0086</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8472,11 +8445,11 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0238</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8513,11 +8486,11 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0425</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8554,11 +8527,11 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0107</v>
+        <v>0.0061</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8595,11 +8568,11 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0443</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8636,11 +8609,11 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.0255</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8677,11 +8650,11 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0337</v>
+        <v>0.0086</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8718,11 +8691,11 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0191</v>
+        <v>0.0061</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8759,11 +8732,11 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0313</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8800,11 +8773,11 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0195</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8841,11 +8814,11 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0156</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8882,11 +8855,11 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0318</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8923,11 +8896,11 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.0408</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8964,11 +8937,11 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0095</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -9005,11 +8978,11 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0436</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9046,11 +9019,11 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.0412</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9087,11 +9060,11 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0155</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9128,11 +9101,11 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0077</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9169,11 +9142,11 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.034</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9210,11 +9183,11 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0272</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9251,11 +9224,11 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.0449</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9292,11 +9265,11 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0341</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9333,11 +9306,11 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0129</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9374,11 +9347,11 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0347</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9415,11 +9388,11 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.0297</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9456,11 +9429,11 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0273</v>
+        <v>0.0238</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9497,11 +9470,11 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0215</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9538,11 +9511,11 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0432</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9579,11 +9552,11 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0186</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9620,11 +9593,11 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.0086</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9661,11 +9634,11 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0328</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9700,24 +9673,20 @@
           <t>P0 - Critical</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0357</v>
+        <v>0.0332</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected valid return type, received mismatched value.</t>
-        </is>
-      </c>
+      <c r="I225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -9747,11 +9716,11 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0242</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9788,11 +9757,11 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9829,11 +9798,11 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0299</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9870,11 +9839,11 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.0255</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9911,11 +9880,11 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0313</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9952,11 +9921,11 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0382</v>
+        <v>0.0134</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9993,11 +9962,11 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0322</v>
+        <v>0.0255</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10034,11 +10003,11 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0361</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10075,11 +10044,11 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0422</v>
+        <v>0.0259</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10116,11 +10085,11 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0132</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10157,11 +10126,11 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0362</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10198,11 +10167,11 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0092</v>
+        <v>0.0225</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10239,11 +10208,11 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.024</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10280,11 +10249,11 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0094</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10321,11 +10290,11 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0265</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10362,11 +10331,11 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0147</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10403,11 +10372,11 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0176</v>
+        <v>0.0203</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10444,11 +10413,11 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0348</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10485,11 +10454,11 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0268</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10526,11 +10495,11 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0148</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10567,11 +10536,11 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0364</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10608,11 +10577,11 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.0278</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10649,11 +10618,11 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0387</v>
+        <v>0.0271</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10690,11 +10659,11 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0296</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10731,11 +10700,11 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10772,11 +10741,11 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0062</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10813,11 +10782,11 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0086</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10854,11 +10823,11 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0184</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10895,11 +10864,11 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0227</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10936,11 +10905,11 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0334</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10977,11 +10946,11 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.041</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11018,11 +10987,11 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0405</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11059,11 +11028,11 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0059</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11100,11 +11069,11 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0357</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11141,11 +11110,11 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.041</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11182,11 +11151,11 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0054</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11223,11 +11192,11 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0091</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11264,11 +11233,11 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0276</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11305,11 +11274,11 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0055</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11346,11 +11315,11 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0056</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11387,11 +11356,11 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0146</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11428,11 +11397,11 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0323</v>
+        <v>0.0068</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11469,11 +11438,11 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0369</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11510,11 +11479,11 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0178</v>
+        <v>0.0203</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11549,24 +11518,20 @@
           <t>P1 - High</t>
         </is>
       </c>
-      <c r="F270" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0339</v>
+        <v>0.0383</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I270" s="2" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected valid return type, received mismatched value.</t>
-        </is>
-      </c>
+      <c r="I270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -11596,11 +11561,11 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0404</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11637,11 +11602,11 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.0291</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11678,11 +11643,11 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0291</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11719,11 +11684,11 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0389</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11760,11 +11725,11 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11801,11 +11766,11 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0075</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11842,11 +11807,11 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.0268</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11883,11 +11848,11 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.045</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11924,11 +11889,11 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.03</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11965,11 +11930,11 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0431</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -12006,11 +11971,11 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0051</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12047,11 +12012,11 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0241</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12088,11 +12053,11 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0251</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12129,11 +12094,11 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0371</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12170,11 +12135,11 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0253</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12211,11 +12176,11 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.0279</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12252,11 +12217,11 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0344</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12293,11 +12258,11 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.038</v>
+        <v>0.0413</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12334,11 +12299,11 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0398</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12375,11 +12340,11 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0387</v>
+        <v>0.0315</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12416,11 +12381,11 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0312</v>
+        <v>0.0104</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12457,11 +12422,11 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0251</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12498,11 +12463,11 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0169</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12539,11 +12504,11 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12580,11 +12545,11 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0381</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12621,11 +12586,11 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0068</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12662,11 +12627,11 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0234</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12703,11 +12668,11 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0368</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12744,11 +12709,11 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0384</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12785,11 +12750,11 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0445</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12826,11 +12791,11 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0404</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-001</t>
+          <t>TC_UNIT_SHA_001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0113</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-002</t>
+          <t>TC_UNIT_SHA_002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.0118</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-003</t>
+          <t>TC_UNIT_SHA_003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0302</v>
+        <v>0.0279</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-004</t>
+          <t>TC_UNIT_SHA_004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0401</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-005</t>
+          <t>TC_UNIT_SHA_005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0272</v>
+        <v>0.0118</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-006</t>
+          <t>TC_UNIT_SHA_006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0186</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-007</t>
+          <t>TC_UNIT_SHA_007</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0407</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-008</t>
+          <t>TC_UNIT_SHA_008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0214</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-009</t>
+          <t>TC_UNIT_SHA_009</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0089</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-010</t>
+          <t>TC_UNIT_SHA_010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0424</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-011</t>
+          <t>TC_UNIT_SHA_011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0381</v>
+        <v>0.0051</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-012</t>
+          <t>TC_UNIT_SHA_012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0179</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-013</t>
+          <t>TC_UNIT_SHA_013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0326</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-014</t>
+          <t>TC_UNIT_SHA_014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0122</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-015</t>
+          <t>TC_UNIT_SHA_015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0331</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-016</t>
+          <t>TC_UNIT_SHA_016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.0433</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-017</t>
+          <t>TC_UNIT_SHA_017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0311</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-018</t>
+          <t>TC_UNIT_SHA_018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0119</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-019</t>
+          <t>TC_UNIT_SHA_019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0238</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-020</t>
+          <t>TC_UNIT_SHA_020</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0178</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-021</t>
+          <t>TC_UNIT_SHA_021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.0223</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-022</t>
+          <t>TC_UNIT_SHA_022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0379</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-023</t>
+          <t>TC_UNIT_SHA_023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0279</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-024</t>
+          <t>TC_UNIT_SHA_024</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0395</v>
+        <v>0.0393</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-025</t>
+          <t>TC_UNIT_SHA_025</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.0415</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-026</t>
+          <t>TC_UNIT_SHA_026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.013</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-027</t>
+          <t>TC_UNIT_SHA_027</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0332</v>
+        <v>0.0092</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-028</t>
+          <t>TC_UNIT_SHA_028</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0356</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-029</t>
+          <t>TC_UNIT_SHA_029</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0195</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-030</t>
+          <t>TC_UNIT_SHA_030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0236</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-031</t>
+          <t>TC_UNIT_SHA_031</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.024</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-032</t>
+          <t>TC_UNIT_SHA_032</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0226</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-033</t>
+          <t>TC_UNIT_SHA_033</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0196</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-034</t>
+          <t>TC_UNIT_SHA_034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0184</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-035</t>
+          <t>TC_UNIT_SHA_035</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.0446</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-036</t>
+          <t>TC_UNIT_SHA_036</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-037</t>
+          <t>TC_UNIT_SHA_037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0328</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-038</t>
+          <t>TC_UNIT_SHA_038</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0081</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-039</t>
+          <t>TC_UNIT_SHA_039</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.0086</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-040</t>
+          <t>TC_UNIT_SHA_040</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0211</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-041</t>
+          <t>TC_UNIT_SHA_041</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.035</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-042</t>
+          <t>TC_UNIT_SHA_042</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0382</v>
+        <v>0.0405</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-043</t>
+          <t>TC_UNIT_SHA_043</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0371</v>
+        <v>0.0186</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-044</t>
+          <t>TC_UNIT_SHA_044</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-045</t>
+          <t>TC_UNIT_SHA_045</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0221</v>
+        <v>0.0424</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-046</t>
+          <t>TC_UNIT_SHA_046</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0259</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-047</t>
+          <t>TC_UNIT_SHA_047</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0051</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-048</t>
+          <t>TC_UNIT_SHA_048</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.0133</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-049</t>
+          <t>TC_UNIT_SHA_049</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0229</v>
+        <v>0.0146</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-050</t>
+          <t>TC_UNIT_SHA_050</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0282</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-051</t>
+          <t>TC_UNIT_SCHEMA_001</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0309</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-052</t>
+          <t>TC_UNIT_SCHEMA_002</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0055</v>
+        <v>0.0218</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-053</t>
+          <t>TC_UNIT_SCHEMA_003</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.0438</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-054</t>
+          <t>TC_UNIT_SCHEMA_004</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0156</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-055</t>
+          <t>TC_UNIT_SCHEMA_005</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0404</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-056</t>
+          <t>TC_UNIT_SCHEMA_006</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0379</v>
+        <v>0.0348</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-057</t>
+          <t>TC_UNIT_SCHEMA_007</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0078</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-058</t>
+          <t>TC_UNIT_SCHEMA_008</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0078</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-059</t>
+          <t>TC_UNIT_SCHEMA_009</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0154</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-060</t>
+          <t>TC_UNIT_SCHEMA_010</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0119</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-061</t>
+          <t>TC_UNIT_SCHEMA_011</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0178</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-062</t>
+          <t>TC_UNIT_SCHEMA_012</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-063</t>
+          <t>TC_UNIT_SCHEMA_013</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0192</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-064</t>
+          <t>TC_UNIT_SCHEMA_014</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.0149</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-065</t>
+          <t>TC_UNIT_SCHEMA_015</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0355</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-066</t>
+          <t>TC_UNIT_SCHEMA_016</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0055</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-067</t>
+          <t>TC_UNIT_SCHEMA_017</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-068</t>
+          <t>TC_UNIT_SCHEMA_018</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.007</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-069</t>
+          <t>TC_UNIT_SCHEMA_019</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.029</v>
+        <v>0.0216</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-070</t>
+          <t>TC_UNIT_SCHEMA_020</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.0302</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-071</t>
+          <t>TC_UNIT_SCHEMA_021</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.024</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-072</t>
+          <t>TC_UNIT_SCHEMA_022</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-073</t>
+          <t>TC_UNIT_SCHEMA_023</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0179</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-074</t>
+          <t>TC_UNIT_SCHEMA_024</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.036</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-075</t>
+          <t>TC_UNIT_SCHEMA_025</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0363</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-076</t>
+          <t>TC_UNIT_SCHEMA_026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.0289</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-077</t>
+          <t>TC_UNIT_SCHEMA_027</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0182</v>
+        <v>0.0304</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-078</t>
+          <t>TC_UNIT_SCHEMA_028</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0316</v>
+        <v>0.0342</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-079</t>
+          <t>TC_UNIT_SCHEMA_029</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.0339</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-080</t>
+          <t>TC_UNIT_SCHEMA_030</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.0252</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-081</t>
+          <t>TC_UNIT_SCHEMA_031</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0168</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-082</t>
+          <t>TC_UNIT_SCHEMA_032</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-083</t>
+          <t>TC_UNIT_SCHEMA_033</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.0374</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-084</t>
+          <t>TC_UNIT_SCHEMA_034</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0137</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-085</t>
+          <t>TC_UNIT_SCHEMA_035</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0078</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-086</t>
+          <t>TC_UNIT_SCHEMA_036</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0247</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-087</t>
+          <t>TC_UNIT_SCHEMA_037</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0407</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-088</t>
+          <t>TC_UNIT_SCHEMA_038</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0334</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-089</t>
+          <t>TC_UNIT_SCHEMA_039</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0065</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-090</t>
+          <t>TC_UNIT_SCHEMA_040</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0067</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-091</t>
+          <t>TC_UNIT_SCHEMA_041</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0445</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-092</t>
+          <t>TC_UNIT_SCHEMA_042</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.013</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-093</t>
+          <t>TC_UNIT_SCHEMA_043</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0277</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-094</t>
+          <t>TC_UNIT_SCHEMA_044</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.0157</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-095</t>
+          <t>TC_UNIT_SCHEMA_045</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0309</v>
+        <v>0.027</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-096</t>
+          <t>TC_UNIT_SCHEMA_046</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0193</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-097</t>
+          <t>TC_UNIT_SCHEMA_047</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.02</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-098</t>
+          <t>TC_UNIT_SCHEMA_048</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.0158</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-099</t>
+          <t>TC_UNIT_SCHEMA_049</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0198</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-100</t>
+          <t>TC_UNIT_SCHEMA_050</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.01</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-101</t>
+          <t>TC_UNIT_REGEX_001</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0428</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-102</t>
+          <t>TC_UNIT_REGEX_002</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0097</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-103</t>
+          <t>TC_UNIT_REGEX_003</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.0449</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-104</t>
+          <t>TC_UNIT_REGEX_004</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-105</t>
+          <t>TC_UNIT_REGEX_005</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.0238</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-106</t>
+          <t>TC_UNIT_REGEX_006</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0376</v>
+        <v>0.0105</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-107</t>
+          <t>TC_UNIT_REGEX_007</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0246</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-108</t>
+          <t>TC_UNIT_REGEX_008</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0065</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-109</t>
+          <t>TC_UNIT_REGEX_009</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0255</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-110</t>
+          <t>TC_UNIT_REGEX_010</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0152</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-111</t>
+          <t>TC_UNIT_REGEX_011</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.0295</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-112</t>
+          <t>TC_UNIT_REGEX_012</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0364</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-113</t>
+          <t>TC_UNIT_REGEX_013</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0445</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-114</t>
+          <t>TC_UNIT_REGEX_014</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.0192</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-115</t>
+          <t>TC_UNIT_REGEX_015</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.0199</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-116</t>
+          <t>TC_UNIT_REGEX_016</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0273</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-117</t>
+          <t>TC_UNIT_REGEX_017</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0271</v>
+        <v>0.0071</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-118</t>
+          <t>TC_UNIT_REGEX_018</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-119</t>
+          <t>TC_UNIT_REGEX_019</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0325</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-120</t>
+          <t>TC_UNIT_REGEX_020</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0311</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-121</t>
+          <t>TC_UNIT_REGEX_021</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0322</v>
+        <v>0.0256</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-122</t>
+          <t>TC_UNIT_REGEX_022</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0081</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-123</t>
+          <t>TC_UNIT_REGEX_023</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.044</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-124</t>
+          <t>TC_UNIT_REGEX_024</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0263</v>
+        <v>0.0081</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-125</t>
+          <t>TC_UNIT_REGEX_025</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0073</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-126</t>
+          <t>TC_UNIT_REGEX_026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0169</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-127</t>
+          <t>TC_UNIT_REGEX_027</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0338</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-128</t>
+          <t>TC_UNIT_REGEX_028</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0435</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-129</t>
+          <t>TC_UNIT_REGEX_029</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0249</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-130</t>
+          <t>TC_UNIT_REGEX_030</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0382</v>
+        <v>0.0206</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-131</t>
+          <t>TC_UNIT_REGEX_031</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.015</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-132</t>
+          <t>TC_UNIT_REGEX_032</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0254</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-133</t>
+          <t>TC_UNIT_REGEX_033</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0448</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-134</t>
+          <t>TC_UNIT_REGEX_034</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.0173</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-135</t>
+          <t>TC_UNIT_REGEX_035</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0154</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-136</t>
+          <t>TC_UNIT_REGEX_036</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0385</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-137</t>
+          <t>TC_UNIT_REGEX_037</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0234</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-138</t>
+          <t>TC_UNIT_REGEX_038</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0387</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-139</t>
+          <t>TC_UNIT_REGEX_039</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0055</v>
+        <v>0.0089</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-140</t>
+          <t>TC_UNIT_REGEX_040</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0411</v>
+        <v>0.0314</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-141</t>
+          <t>TC_UNIT_REGEX_041</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0097</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-142</t>
+          <t>TC_UNIT_REGEX_042</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0225</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-143</t>
+          <t>TC_UNIT_REGEX_043</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0227</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-144</t>
+          <t>TC_UNIT_REGEX_044</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0164</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-145</t>
+          <t>TC_UNIT_REGEX_045</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0396</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-146</t>
+          <t>TC_UNIT_REGEX_046</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0413</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-147</t>
+          <t>TC_UNIT_REGEX_047</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0104</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-148</t>
+          <t>TC_UNIT_REGEX_048</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0358</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-149</t>
+          <t>TC_UNIT_REGEX_049</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0426</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-150</t>
+          <t>TC_UNIT_REGEX_050</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0182</v>
+        <v>0.0243</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-151</t>
+          <t>TC_UNIT_JWT_001</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0165</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-152</t>
+          <t>TC_UNIT_JWT_002</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.0065</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-153</t>
+          <t>TC_UNIT_JWT_003</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0098</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-154</t>
+          <t>TC_UNIT_JWT_004</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0103</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-155</t>
+          <t>TC_UNIT_JWT_005</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.0276</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-156</t>
+          <t>TC_UNIT_JWT_006</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0258</v>
+        <v>0.0152</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-157</t>
+          <t>TC_UNIT_JWT_007</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0126</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-158</t>
+          <t>TC_UNIT_JWT_008</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-159</t>
+          <t>TC_UNIT_JWT_009</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0213</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-160</t>
+          <t>TC_UNIT_JWT_010</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0146</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-161</t>
+          <t>TC_UNIT_JWT_011</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0292</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-162</t>
+          <t>TC_UNIT_JWT_012</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.0325</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-163</t>
+          <t>TC_UNIT_JWT_013</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0229</v>
+        <v>0.0198</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-164</t>
+          <t>TC_UNIT_JWT_014</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.03</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-165</t>
+          <t>TC_UNIT_JWT_015</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0213</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-166</t>
+          <t>TC_UNIT_JWT_016</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.0399</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-167</t>
+          <t>TC_UNIT_JWT_017</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0122</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-168</t>
+          <t>TC_UNIT_JWT_018</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0364</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-169</t>
+          <t>TC_UNIT_JWT_019</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.0073</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-170</t>
+          <t>TC_UNIT_JWT_020</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.0186</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-171</t>
+          <t>TC_UNIT_JWT_021</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.017</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-172</t>
+          <t>TC_UNIT_JWT_022</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0274</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-173</t>
+          <t>TC_UNIT_JWT_023</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0263</v>
+        <v>0.0405</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-174</t>
+          <t>TC_UNIT_JWT_024</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0358</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-175</t>
+          <t>TC_UNIT_JWT_025</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.028</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-176</t>
+          <t>TC_UNIT_JWT_026</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0326</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-177</t>
+          <t>TC_UNIT_JWT_027</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.0201</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-178</t>
+          <t>TC_UNIT_JWT_028</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.023</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-179</t>
+          <t>TC_UNIT_JWT_029</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0356</v>
+        <v>0.0289</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-180</t>
+          <t>TC_UNIT_JWT_030</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0278</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-181</t>
+          <t>TC_UNIT_JWT_031</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0347</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-182</t>
+          <t>TC_UNIT_JWT_032</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0189</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-183</t>
+          <t>TC_UNIT_JWT_033</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0229</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-184</t>
+          <t>TC_UNIT_JWT_034</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.011</v>
+        <v>0.0347</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-185</t>
+          <t>TC_UNIT_JWT_035</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0144</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-186</t>
+          <t>TC_UNIT_JWT_036</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0442</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-187</t>
+          <t>TC_UNIT_JWT_037</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0301</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-188</t>
+          <t>TC_UNIT_JWT_038</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0117</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-189</t>
+          <t>TC_UNIT_JWT_039</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0181</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-190</t>
+          <t>TC_UNIT_JWT_040</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.015</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-191</t>
+          <t>TC_UNIT_JWT_041</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0433</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-192</t>
+          <t>TC_UNIT_JWT_042</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0406</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-193</t>
+          <t>TC_UNIT_JWT_043</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.007</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-194</t>
+          <t>TC_UNIT_JWT_044</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0208</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-195</t>
+          <t>TC_UNIT_JWT_045</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0425</v>
+        <v>0.0336</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-196</t>
+          <t>TC_UNIT_JWT_046</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0439</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-197</t>
+          <t>TC_UNIT_JWT_047</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0221</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-198</t>
+          <t>TC_UNIT_JWT_048</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0287</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-199</t>
+          <t>TC_UNIT_JWT_049</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0071</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-200</t>
+          <t>TC_UNIT_JWT_050</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.021</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-201</t>
+          <t>TC_UNIT_RBAC_001</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0219</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-202</t>
+          <t>TC_UNIT_RBAC_002</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.026</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-203</t>
+          <t>TC_UNIT_RBAC_003</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0325</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-204</t>
+          <t>TC_UNIT_RBAC_004</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0293</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-205</t>
+          <t>TC_UNIT_RBAC_005</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.0405</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-206</t>
+          <t>TC_UNIT_RBAC_006</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0201</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-207</t>
+          <t>TC_UNIT_RBAC_007</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0357</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-208</t>
+          <t>TC_UNIT_RBAC_008</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.0379</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-209</t>
+          <t>TC_UNIT_RBAC_009</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0269</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-210</t>
+          <t>TC_UNIT_RBAC_010</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.029</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-211</t>
+          <t>TC_UNIT_RBAC_011</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0242</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-212</t>
+          <t>TC_UNIT_RBAC_012</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0291</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-213</t>
+          <t>TC_UNIT_RBAC_013</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0449</v>
+        <v>0.0207</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-214</t>
+          <t>TC_UNIT_RBAC_014</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0407</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-215</t>
+          <t>TC_UNIT_RBAC_015</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0304</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-216</t>
+          <t>TC_UNIT_RBAC_016</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0192</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-217</t>
+          <t>TC_UNIT_RBAC_017</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0345</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-218</t>
+          <t>TC_UNIT_RBAC_018</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0155</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-219</t>
+          <t>TC_UNIT_RBAC_019</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0215</v>
+        <v>0.0233</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-220</t>
+          <t>TC_UNIT_RBAC_020</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0333</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-221</t>
+          <t>TC_UNIT_RBAC_021</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0433</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-222</t>
+          <t>TC_UNIT_RBAC_022</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0195</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-223</t>
+          <t>TC_UNIT_RBAC_023</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0344</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-224</t>
+          <t>TC_UNIT_RBAC_024</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0332</v>
+        <v>0.0114</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-225</t>
+          <t>TC_UNIT_RBAC_025</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0143</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-226</t>
+          <t>TC_UNIT_RBAC_026</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-227</t>
+          <t>TC_UNIT_RBAC_027</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0128</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-228</t>
+          <t>TC_UNIT_RBAC_028</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0205</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-229</t>
+          <t>TC_UNIT_RBAC_029</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.007</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-230</t>
+          <t>TC_UNIT_RBAC_030</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0134</v>
+        <v>0.0401</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-231</t>
+          <t>TC_UNIT_RBAC_031</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0059</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-232</t>
+          <t>TC_UNIT_RBAC_032</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0361</v>
+        <v>0.0294</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-233</t>
+          <t>TC_UNIT_RBAC_033</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0233</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-234</t>
+          <t>TC_UNIT_RBAC_034</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0443</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-235</t>
+          <t>TC_UNIT_RBAC_035</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0418</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-236</t>
+          <t>TC_UNIT_RBAC_036</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0255</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-237</t>
+          <t>TC_UNIT_RBAC_037</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0127</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-238</t>
+          <t>TC_UNIT_RBAC_038</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.0249</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-239</t>
+          <t>TC_UNIT_RBAC_039</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0265</v>
+        <v>0.0061</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-240</t>
+          <t>TC_UNIT_RBAC_040</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.0326</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-241</t>
+          <t>TC_UNIT_RBAC_041</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0171</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-242</t>
+          <t>TC_UNIT_RBAC_042</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.021</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-243</t>
+          <t>TC_UNIT_RBAC_043</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0352</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-244</t>
+          <t>TC_UNIT_RBAC_044</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0106</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-245</t>
+          <t>TC_UNIT_RBAC_045</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0367</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-246</t>
+          <t>TC_UNIT_RBAC_046</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.0388</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-247</t>
+          <t>TC_UNIT_RBAC_047</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0271</v>
+        <v>0.0307</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-248</t>
+          <t>TC_UNIT_RBAC_048</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0296</v>
+        <v>0.0393</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-249</t>
+          <t>TC_UNIT_RBAC_049</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0109</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-250</t>
+          <t>TC_UNIT_RBAC_050</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0247</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-251</t>
+          <t>TC_UNIT_UTIL_001</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0222</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-252</t>
+          <t>TC_UNIT_UTIL_002</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.034</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-253</t>
+          <t>TC_UNIT_UTIL_003</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.006</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-254</t>
+          <t>TC_UNIT_UTIL_004</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0334</v>
+        <v>0.0367</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-255</t>
+          <t>TC_UNIT_UTIL_005</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0065</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-256</t>
+          <t>TC_UNIT_UTIL_006</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0378</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-257</t>
+          <t>TC_UNIT_UTIL_007</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0271</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-258</t>
+          <t>TC_UNIT_UTIL_008</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0357</v>
+        <v>0.0145</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-259</t>
+          <t>TC_UNIT_UTIL_009</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0255</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-260</t>
+          <t>TC_UNIT_UTIL_010</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0335</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-261</t>
+          <t>TC_UNIT_UTIL_011</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0083</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-262</t>
+          <t>TC_UNIT_UTIL_012</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0276</v>
+        <v>0.0308</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-263</t>
+          <t>TC_UNIT_UTIL_013</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0055</v>
+        <v>0.0328</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-264</t>
+          <t>TC_UNIT_UTIL_014</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0056</v>
+        <v>0.0332</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-265</t>
+          <t>TC_UNIT_UTIL_015</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0071</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-266</t>
+          <t>TC_UNIT_UTIL_016</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0218</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-267</t>
+          <t>TC_UNIT_UTIL_017</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0369</v>
+        <v>0.0375</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-268</t>
+          <t>TC_UNIT_UTIL_018</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0291</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-269</t>
+          <t>TC_UNIT_UTIL_019</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0189</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-270</t>
+          <t>TC_UNIT_UTIL_020</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.0377</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-271</t>
+          <t>TC_UNIT_UTIL_021</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0196</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-272</t>
+          <t>TC_UNIT_UTIL_022</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0355</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-273</t>
+          <t>TC_UNIT_UTIL_023</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0203</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-274</t>
+          <t>TC_UNIT_UTIL_024</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.021</v>
+        <v>0.0413</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-275</t>
+          <t>TC_UNIT_UTIL_025</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0365</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-276</t>
+          <t>TC_UNIT_UTIL_026</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-277</t>
+          <t>TC_UNIT_UTIL_027</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.045</v>
+        <v>0.0123</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-278</t>
+          <t>TC_UNIT_UTIL_028</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-279</t>
+          <t>TC_UNIT_UTIL_029</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.01</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-280</t>
+          <t>TC_UNIT_UTIL_030</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0144</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-281</t>
+          <t>TC_UNIT_UTIL_031</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.0432</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-282</t>
+          <t>TC_UNIT_UTIL_032</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0343</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-283</t>
+          <t>TC_UNIT_UTIL_033</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0371</v>
+        <v>0.0277</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-284</t>
+          <t>TC_UNIT_UTIL_034</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0102</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-285</t>
+          <t>TC_UNIT_UTIL_035</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0091</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-286</t>
+          <t>TC_UNIT_UTIL_036</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0358</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-287</t>
+          <t>TC_UNIT_UTIL_037</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0413</v>
+        <v>0.0144</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-288</t>
+          <t>TC_UNIT_UTIL_038</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.0385</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-289</t>
+          <t>TC_UNIT_UTIL_039</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.0111</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-290</t>
+          <t>TC_UNIT_UTIL_040</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0208</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-291</t>
+          <t>TC_UNIT_UTIL_041</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0172</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-292</t>
+          <t>TC_UNIT_UTIL_042</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0223</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-293</t>
+          <t>TC_UNIT_UTIL_043</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0279</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-294</t>
+          <t>TC_UNIT_UTIL_044</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0381</v>
+        <v>0.0339</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-295</t>
+          <t>TC_UNIT_UTIL_045</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0342</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-296</t>
+          <t>TC_UNIT_UTIL_046</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0234</v>
+        <v>0.0252</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-297</t>
+          <t>TC_UNIT_UTIL_047</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0139</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-298</t>
+          <t>TC_UNIT_UTIL_048</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0303</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-299</t>
+          <t>TC_UNIT_UTIL_049</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0176</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>TC-UNIT-300</t>
+          <t>TC_UNIT_UTIL_050</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.0187</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.044</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0441</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0158</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0113</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0215</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0359</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0375</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0387</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0141</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0377</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0066</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.0153</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0239</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0411</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0441</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0129</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0269</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0095</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0178</v>
+        <v>0.0076</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0233</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0379</v>
+        <v>0.0237</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0098</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0342</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.0199</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.013</v>
+        <v>0.0123</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0092</v>
+        <v>0.0326</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0356</v>
+        <v>0.0417</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0354</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0307</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0346</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0129</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0403</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.0365</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.015</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0426</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0167</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0428</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.02</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0211</v>
+        <v>0.0384</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.035</v>
+        <v>0.0439</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0265</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0054</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0418</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0277</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0442</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0419</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0074</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0122</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0309</v>
+        <v>0.038</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0151</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0438</v>
+        <v>0.0152</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0103</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.0166</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0335</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0078</v>
+        <v>0.0289</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0078</v>
+        <v>0.0114</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0117</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.044</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.0178</v>
+        <v>0.044</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0118</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.0282</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0149</v>
+        <v>0.0377</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.0341</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0055</v>
+        <v>0.0131</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0269</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0181</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.031</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0302</v>
+        <v>0.0418</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0188</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.0372</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0418</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.0352</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0219</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.023</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.011</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0339</v>
+        <v>0.0058</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0252</v>
+        <v>0.0416</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0168</v>
+        <v>0.0275</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0202</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0374</v>
+        <v>0.0436</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0338</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0078</v>
+        <v>0.0366</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0212</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0153</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0334</v>
+        <v>0.0384</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0407</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0327</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0157</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.013</v>
+        <v>0.0231</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0388</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0126</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0226</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0446</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0441</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0207</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0385</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0384</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0262</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0449</v>
+        <v>0.0213</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.033</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0226</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0253</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0223</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0256</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0199</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0128</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.0081</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0071</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.007</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.0435</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.032</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0273</v>
+        <v>0.0229</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0105</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0192</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0135</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0176</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0161</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0163</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.044</v>
+        <v>0.0256</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0383</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.0371</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0194</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0291</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.007</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0361</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0172</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0142</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0254</v>
+        <v>0.0239</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0448</v>
+        <v>0.0322</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0338</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0237</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0424</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0234</v>
+        <v>0.0144</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0387</v>
+        <v>0.0412</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0277</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0136</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0201</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0227</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0304</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0067</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0307</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0277</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.028</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.0375</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.0209</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0164</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.0168</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.0331</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0276</v>
+        <v>0.017</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0299</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0255</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.0225</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0397</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.0341</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0218</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0314</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0441</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.0394</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0403</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.0106</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0294</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.0156</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0388</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0361</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.011</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0354</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0438</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0329</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.0218</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0163</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0233</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.0061</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0438</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0192</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0229</v>
+        <v>0.0264</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0195</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0213</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0224</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.0445</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0226</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0195</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.015</v>
+        <v>0.041</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0378</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0406</v>
+        <v>0.0432</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0203</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0247</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0133</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0189</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0221</v>
+        <v>0.0407</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0135</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0299</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.021</v>
+        <v>0.0277</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0436</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0254</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0138</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0293</v>
+        <v>0.0223</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0226</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.0187</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0357</v>
+        <v>0.0208</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0379</v>
+        <v>0.0378</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0277</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.029</v>
+        <v>0.0312</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0216</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0444</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0083</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0294</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.0318</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.0225</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.043</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0106</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0336</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.0067</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.016</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0072</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0227</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0288</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0143</v>
+        <v>0.0412</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.037</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0377</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.0067</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0307</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0161</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0274</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0184</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.032</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0111</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0054</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0349</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.0218</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0262</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0343</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0144</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.022</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.021</v>
+        <v>0.0175</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.024</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0225</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0377</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.035</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0397</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0225</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.0075</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0123</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0222</v>
+        <v>0.0127</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0203</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0344</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0314</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.024</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0119</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0271</v>
+        <v>0.0372</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0374</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0202</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0119</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0232</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0098</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0139</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0332</v>
+        <v>0.0284</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0349</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0204</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0197</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0421</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0157</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0176</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0351</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.045</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.005</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0413</v>
+        <v>0.0261</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.007</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0186</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0287</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.04</v>
+        <v>0.0375</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0167</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0229</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.011</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0343</v>
+        <v>0.0193</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0196</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0073</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.045</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0284</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0112</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0366</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0278</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0162</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0204</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.039</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0339</v>
+        <v>0.0357</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.0333</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0252</v>
+        <v>0.0069</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0421</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0115</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0176</v>
+        <v>0.039</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0317</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.044</v>
+        <v>0.0299</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0445</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0441</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.0417</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0215</v>
+        <v>0.02</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0112</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0393</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0387</v>
+        <v>0.0428</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0315</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0316</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0392</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0446</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.0397</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0366</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0411</v>
+        <v>0.0294</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0173</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0407</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0124</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0416</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0227</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0097</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0437</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.0151</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.0182</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0419</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0256</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0064</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0215</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0354</v>
+        <v>0.0257</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0218</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0281</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0414</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0386</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0321</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0393</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0167</v>
+        <v>0.0399</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0095</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0236</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0071</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0265</v>
+        <v>0.0335</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0407</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0278</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0192</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0059</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0245</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0419</v>
+        <v>0.0112</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.0207</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.0351</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.038</v>
+        <v>0.0161</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0061</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.0177</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0372</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0408</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0255</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0243</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0281</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.044</v>
+        <v>0.0328</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.044</v>
+        <v>0.039</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0118</v>
+        <v>0.0194</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0222</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0214</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0363</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0228</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0445</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0389</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.031</v>
+        <v>0.0303</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0326</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.0333</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.028</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0283</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0258</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0062</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0237</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0172</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.011</v>
+        <v>0.0186</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0126</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0114</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0335</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0121</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0102</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0314</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.0391</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0429</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.005</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0274</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.0408</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0412</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0094</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.0416</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0299</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0414</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0353</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0074</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0126</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.04</v>
+        <v>0.0113</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0358</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0197</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.0417</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0234</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0133</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0359</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0292</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0142</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0251</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0231</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0074</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0077</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0185</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0449</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.032</v>
+        <v>0.0284</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0229</v>
+        <v>0.024</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0366</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.031</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0374</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0176</v>
+        <v>0.0264</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0349</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0365</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0056</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0169</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0371</v>
+        <v>0.0299</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0104</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0135</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0199</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0361</v>
+        <v>0.0232</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0391</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.0278</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.0164</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0322</v>
+        <v>0.0369</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0355</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0264</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0324</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.0116</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0194</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.0054</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0332</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.0363</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0379</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0095</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0159</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0301</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0102</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0217</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0408</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0209</v>
+        <v>0.0359</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0375</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0168</v>
+        <v>0.0156</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0421</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0268</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0154</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0335</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0288</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0299</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0446</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0209</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0081</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0105</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0394</v>
+        <v>0.019</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0068</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.005</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0103</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0193</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.0247</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0361</v>
+        <v>0.0247</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0354</v>
+        <v>0.0341</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0438</v>
+        <v>0.0371</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0372</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0329</v>
+        <v>0.024</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0132</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.014</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0243</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.041</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0438</v>
+        <v>0.0189</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.036</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0321</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0261</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.0133</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0389</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0282</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0154</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0279</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0383</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0352</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0344</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0151</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.025</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0387</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0372</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0423</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0067</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0431</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0266</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0348</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0254</v>
+        <v>0.0219</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.0231</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0063</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0226</v>
+        <v>0.0172</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0269</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0158</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0201</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0146</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.0312</v>
+        <v>0.013</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0403</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0444</v>
+        <v>0.0182</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0389</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0348</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0132</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0346</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0142</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0343</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0388</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.016</v>
+        <v>0.0257</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0151</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0306</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.0347</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.0112</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.037</v>
+        <v>0.0094</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0243</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0062</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0143</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0207</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.0147</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.0198</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.032</v>
+        <v>0.0315</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0132</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0331</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0349</v>
+        <v>0.0352</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.02</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0444</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0343</v>
+        <v>0.0302</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0287</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.022</v>
+        <v>0.0298</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0175</v>
+        <v>0.0369</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.024</v>
+        <v>0.034</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0389</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0132</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.035</v>
+        <v>0.0238</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0125</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0083</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0432</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.0156</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0148</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0403</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.043</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0416</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.04</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0213</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0374</v>
+        <v>0.0145</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0062</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0095</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0232</v>
+        <v>0.0313</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.018</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0346</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0429</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0257</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0148</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0156</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0176</v>
+        <v>0.0395</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0207</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.045</v>
+        <v>0.0317</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0222</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0442</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0218</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0166</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0301</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0167</v>
+        <v>0.0302</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0229</v>
+        <v>0.0416</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.011</v>
+        <v>0.0385</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0141</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0403</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.0438</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.045</v>
+        <v>0.0425</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0349</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0342</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.0445</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0237</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.0291</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0128</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0422</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0095</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0357</v>
+        <v>0.0158</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.0408</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0437</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0421</v>
+        <v>0.0325</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0144</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0333</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0203</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0314</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0292</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0348</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0161</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.037</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0264</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0206</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.0386</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0316</v>
+        <v>0.0053</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0051</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0066</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0215</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0297</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0287</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0204</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0091</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.0077</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0262</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.0341</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0306</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.015</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0397</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0182</v>
+        <v>0.0271</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0419</v>
+        <v>0.0217</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0396</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.034</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0215</v>
+        <v>0.0287</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.01</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.0225</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0235</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0201</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0313</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0188</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0187</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.015</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0194</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0162</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0249</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0364</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0355</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.027</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0192</v>
+        <v>0.0173</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0059</v>
+        <v>0.0083</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0281</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.028</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0138</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0066</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0202</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0237</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.0233</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0177</v>
+        <v>0.0123</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0057</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.023</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0065</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.025</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0432</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0409</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.039</v>
+        <v>0.042</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0275</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0222</v>
+        <v>0.0337</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.03</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.0291</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0253</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0081</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0112</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0055</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.035</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0081</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0283</v>
+        <v>0.0095</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.0258</v>
+        <v>0.041</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0353</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0112</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0117</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0206</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0228</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0415</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.04</v>
+        <v>0.0275</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.038</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0121</v>
+        <v>0.0278</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0238</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0251</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0391</v>
+        <v>0.0315</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.0265</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0129</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.0068</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.0374</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.0312</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0091</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0318</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0393</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.025</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.039</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0398</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0194</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.039</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0257</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0446</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0307</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0234</v>
+        <v>0.0429</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0295</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0256</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.037</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.0301</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0447</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0254</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.0368</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0265</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.0294</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0449</v>
+        <v>0.0319</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0385</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0261</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.031</v>
+        <v>0.0428</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0374</v>
+        <v>0.0146</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0289</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0349</v>
+        <v>0.0279</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0056</v>
+        <v>0.0205</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0054</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0066</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0292</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.018</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.043</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0232</v>
+        <v>0.0179</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0391</v>
+        <v>0.0239</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0289</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0369</v>
+        <v>0.0447</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0414</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.0401</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0233</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0338</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0187</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.043</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0236</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0332</v>
+        <v>0.038</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.0052</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0379</v>
+        <v>0.032</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0398</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0135</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.0383</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0065</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0145</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.0255</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0262</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0185</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0429</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0421</v>
+        <v>0.0287</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0385</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0202</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0427</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.0432</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0123</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0126</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0209</v>
+        <v>0.0258</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0173</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0428</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.019</v>
+        <v>0.0268</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0346</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.005</v>
+        <v>0.0313</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.0291</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0291</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0313</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0086</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0367</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0371</v>
+        <v>0.0319</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0162</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0144</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0393</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.0156</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0307</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0384</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.036</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0443</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0246</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0211</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0199</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0105</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0166</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0421</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0323</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0053</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0062</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0247</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0269</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0387</v>
+        <v>0.0174</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0202</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.0283</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0073</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0245</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0311</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0415</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0219</v>
+        <v>0.0357</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0407</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0198</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0193</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0347</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.011</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0086</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.013</v>
+        <v>0.0169</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0273</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0182</v>
+        <v>0.0443</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0253</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0058</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0115</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0196</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.0325</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0196</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0343</v>
+        <v>0.0072</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.0398</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.0305</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0208</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0181</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.0308</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.0146</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.0077</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0154</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0143</v>
+        <v>0.0328</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0095</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.031</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0266</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.0292</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0114</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0336</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0402</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0359</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0444</v>
+        <v>0.0126</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0302</v>
+        <v>0.0375</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0435</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0298</v>
+        <v>0.0395</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0369</v>
+        <v>0.0195</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0095</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0172</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0436</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0172</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.0116</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0287</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.034</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0177</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0062</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0379</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0368</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0137</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0236</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.04</v>
+        <v>0.0121</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.0277</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0306</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0174</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0365</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0358</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.018</v>
+        <v>0.0391</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0267</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.0133</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.0392</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.0207</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0189</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0421</v>
+        <v>0.0296</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0166</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0395</v>
+        <v>0.041</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0384</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0409</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0446</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0222</v>
+        <v>0.0449</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0265</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.017</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0295</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.0323</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0302</v>
+        <v>0.0286</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0174</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0114</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0385</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0382</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0438</v>
+        <v>0.0319</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0425</v>
+        <v>0.0157</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0349</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.0102</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0212</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0069</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0343</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0128</v>
+        <v>0.0363</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0422</v>
+        <v>0.0264</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0177</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0217</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.0415</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0051</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0135</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0092</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.0233</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0265</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.028</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.0423</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0351</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0274</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0285</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.037</v>
+        <v>0.0328</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0162</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0241</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0237</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0134</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0253</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0448</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0215</v>
+        <v>0.0339</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0399</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0424</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0194</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0235</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.008</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0212</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.022</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0206</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0337</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0448</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0271</v>
+        <v>0.0287</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0262</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0131</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0378</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0363</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0246</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.0212</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0328</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.016</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0272</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.0283</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.042</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0352</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0399</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0171</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0189</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0432</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0232</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0434</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.0299</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0223</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0279</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0243</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.032</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0146</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.0197</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0333</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0414</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0318</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0433</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0116</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0057</v>
+        <v>0.0376</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0169</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0201</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0151</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.006</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0244</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.042</v>
+        <v>0.026</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0427</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0337</v>
+        <v>0.0106</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0274</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0163</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0138</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0172</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0155</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.0252</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0055</v>
+        <v>0.0415</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.035</v>
+        <v>0.0249</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0174</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0116</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.041</v>
+        <v>0.024</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.0324</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.0122</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0307</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0366</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.023</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0108</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.038</v>
+        <v>0.0437</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0278</v>
+        <v>0.0239</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0274</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0251</v>
+        <v>0.0393</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0315</v>
+        <v>0.02</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0265</v>
+        <v>0.0308</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0392</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0437</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0374</v>
+        <v>0.0414</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0312</v>
+        <v>0.024</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0147</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0303</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0337</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0109</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0306</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.0417</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0181</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0094</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.0058</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0301</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0396</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.0089</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.0274</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0434</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.033</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0392</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0254</v>
+        <v>0.0365</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0174</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0265</v>
+        <v>0.0433</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0314</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0319</v>
+        <v>0.0281</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0147</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0217</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0261</v>
+        <v>0.0434</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0283</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0177</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0051</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0345</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0224</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.0301</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0066</v>
+        <v>0.0398</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.0441</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.018</v>
+        <v>0.037</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0268</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.0091</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.008</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0435</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0355</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.012</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.031</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0181</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0134</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0098</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.039</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0367</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0439</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0328</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.038</v>
+        <v>0.0381</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0344</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.032</v>
+        <v>0.0133</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.0234</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0058</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.022</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0201</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0364</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0097</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0305</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.0141</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.0321</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0418</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.011</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0427</v>
+        <v>0.0375</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0325</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0392</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0294</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0215</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0258</v>
+        <v>0.0336</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0104</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0142</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0221</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0336</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0196</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0205</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0291</v>
+        <v>0.0113</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0215</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0284</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0366</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0399</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0319</v>
+        <v>0.0359</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0194</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0248</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0186</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.014</v>
+        <v>0.0139</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0392</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0253</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0336</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0413</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0403</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0367</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0211</v>
+        <v>0.0447</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0156</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.014</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0171</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0421</v>
+        <v>0.0256</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.0323</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0071</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0095</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0081</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0399</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0243</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0067</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0283</v>
+        <v>0.0279</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0073</v>
+        <v>0.0319</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0125</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0275</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.0256</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0357</v>
+        <v>0.0158</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.0385</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0295</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0324</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0269</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.011</v>
+        <v>0.021</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0221</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0218</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0273</v>
+        <v>0.0427</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0266</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0204</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0321</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0197</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.037</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0273</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0242</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0423</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.0081</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0305</v>
+        <v>0.0062</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0137</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0435</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0425</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0211</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.007</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0057</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0378</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0396</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0092</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.031</v>
+        <v>0.016</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0267</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.0153</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0342</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0259</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0402</v>
+        <v>0.0223</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0385</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0091</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0305</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0426</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0395</v>
+        <v>0.0071</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0149</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0257</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0148</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0166</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0368</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0173</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0426</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0217</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0177</v>
+        <v>0.0075</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0318</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0379</v>
+        <v>0.0314</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0432</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0253</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0327</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0121</v>
+        <v>0.0162</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0109</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0428</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0417</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0143</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0391</v>
+        <v>0.0273</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.0114</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0308</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0235</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.027</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0329</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0296</v>
+        <v>0.0288</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0439</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0101</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0286</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0445</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.037</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0449</v>
+        <v>0.0352</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0265</v>
+        <v>0.0418</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0397</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.0123</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.0323</v>
+        <v>0.0397</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.0063</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0317</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0395</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0289</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0382</v>
+        <v>0.0447</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0319</v>
+        <v>0.0125</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0086</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0253</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0236</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.029</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0255</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0343</v>
+        <v>0.0324</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.0223</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0271</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0177</v>
+        <v>0.0273</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0199</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.0119</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0129</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0135</v>
+        <v>0.0314</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0092</v>
+        <v>0.017</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0316</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0265</v>
+        <v>0.0089</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0364</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.043</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0425</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0285</v>
+        <v>0.0295</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0163</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0311</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.0069</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0423</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0134</v>
+        <v>0.0196</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0336</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0448</v>
+        <v>0.0338</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0339</v>
+        <v>0.028</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.01</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0446</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0326</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0174</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.008</v>
+        <v>0.0248</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.022</v>
+        <v>0.042</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0245</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0337</v>
+        <v>0.0344</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0448</v>
+        <v>0.0062</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0213</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0214</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0159</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0198</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.034</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.035</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.0263</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0365</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.016</v>
+        <v>0.0324</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0272</v>
+        <v>0.0162</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0283</v>
+        <v>0.0166</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0238</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0412</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0424</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.025</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0329</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0136</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0232</v>
+        <v>0.01</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0187</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0307</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0201</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0443</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.0341</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.032</v>
+        <v>0.0067</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0364</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0298</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.0391</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0361</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0247</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0404</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0143</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0376</v>
+        <v>0.0269</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0383</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.0293</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0348</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.006</v>
+        <v>0.0441</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.0438</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0277</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0427</v>
+        <v>0.0358</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0106</v>
+        <v>0.0304</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.0058</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0124</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.0183</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0279</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0293</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0252</v>
+        <v>0.0199</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.0134</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0249</v>
+        <v>0.0054</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0389</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0248</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0184</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0435</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0122</v>
+        <v>0.0127</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0255</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0207</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.023</v>
+        <v>0.0112</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.0409</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0189</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.041</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.0105</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0164</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.02</v>
+        <v>0.0094</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.036</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0394</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0282</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0124</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0368</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.0292</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.0056</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0237</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0337</v>
+        <v>0.0422</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.008</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.022</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0159</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0076</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.0217</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0379</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.0351</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0377</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0056</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.026</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0193</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.012</v>
+        <v>0.0362</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0156</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0116</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.039</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0399</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0433</v>
+        <v>0.0212</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0248</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0281</v>
+        <v>0.0307</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0147</v>
+        <v>0.0287</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0424</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0129</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.0283</v>
+        <v>0.0188</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0177</v>
+        <v>0.0342</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0437</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.0202</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.03</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.0266</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0426</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.0126</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0407</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.037</v>
+        <v>0.0353</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0246</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0428</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.008</v>
+        <v>0.0064</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0342</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0355</v>
+        <v>0.0266</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.012</v>
+        <v>0.0394</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.031</v>
+        <v>0.0074</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0253</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0134</v>
+        <v>0.015</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.0189</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0238</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0267</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0378</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0405</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0381</v>
+        <v>0.034</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0144</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0259</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0234</v>
+        <v>0.036</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0115</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.018</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0282</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0305</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0358</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0316</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.011</v>
+        <v>0.0125</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0259</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0231</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0068</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0441</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0272</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0215</v>
+        <v>0.0365</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0157</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0204</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0142</v>
+        <v>0.027</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0221</v>
+        <v>0.035</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0299</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.039</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.0323</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.0394</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0215</v>
+        <v>0.0319</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0149</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0163</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0335</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0359</v>
+        <v>0.0064</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0228</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.0097</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.026</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0248</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0319</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0444</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0176</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0413</v>
+        <v>0.0414</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0434</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0198</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0224</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0075</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.014</v>
+        <v>0.0434</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.0405</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0406</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0173</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0053</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0095</v>
+        <v>0.0419</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0298</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0299</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0243</v>
+        <v>0.0347</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0102</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.041</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0319</v>
+        <v>0.0172</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.039</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0276</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0158</v>
+        <v>0.0115</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0356</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.02</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0311</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0429</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0277</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.021</v>
+        <v>0.0386</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0221</v>
+        <v>0.0196</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.0218</v>
+        <v>0.017</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0427</v>
+        <v>0.015</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0214</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0198</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.0186</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0091</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.037</v>
+        <v>0.0188</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0273</v>
+        <v>0.0164</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.0306</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.0284</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0081</v>
+        <v>0.0206</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0149</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0233</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0299</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0425</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0211</v>
+        <v>0.0245</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.007</v>
+        <v>0.0423</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0057</v>
+        <v>0.0274</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0345</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0061</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0092</v>
+        <v>0.0236</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.016</v>
+        <v>0.0381</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.0435</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0282</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.032</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0415</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0303</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0119</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0155</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0305</v>
+        <v>0.038</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0385</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0071</v>
+        <v>0.0204</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0149</v>
+        <v>0.0449</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.0349</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0264</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0111</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0378</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0252</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0223</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0382</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.0353</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0058</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0064</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0334</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0339</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.0209</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0384</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0109</v>
+        <v>0.0295</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0411</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0228</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0339</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0143</v>
+        <v>0.0285</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0273</v>
+        <v>0.042</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.026</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0065</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0235</v>
+        <v>0.0157</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0246</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0329</v>
+        <v>0.0326</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.033</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0077</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0161</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.0376</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0134</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.037</v>
+        <v>0.0363</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0424</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0194</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0257</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0151</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.0397</v>
+        <v>0.0191</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0132</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0317</v>
+        <v>0.0352</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0395</v>
+        <v>0.0349</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0289</v>
+        <v>0.0394</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0152</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.0285</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.0388</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0325</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0439</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.029</v>
+        <v>0.0276</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0139</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0279</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0279</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0271</v>
+        <v>0.0402</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0273</v>
+        <v>0.0102</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0334</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0428</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.017</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0331</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0198</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0316</v>
+        <v>0.0418</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0307</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0276</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0417</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0425</v>
+        <v>0.03</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0231</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0295</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0419</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.0377</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0399</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0314</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0131</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.028</v>
+        <v>0.0295</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0074</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0414</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0392</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.0175</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0429</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0447</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0426</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0344</v>
+        <v>0.0072</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0062</v>
+        <v>0.0105</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0213</v>
+        <v>0.0186</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0287</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0154</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0396</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0072</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.035</v>
+        <v>0.0161</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0263</v>
+        <v>0.0189</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0325</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0272</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0241</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0166</v>
+        <v>0.0306</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0146</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0412</v>
+        <v>0.0288</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0306</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0275</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0329</v>
+        <v>0.0069</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.0216</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.01</v>
+        <v>0.0372</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0236</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0196</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.0224</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0443</v>
+        <v>0.0133</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.0234</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0067</v>
+        <v>0.0259</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0364</v>
+        <v>0.0222</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0298</v>
+        <v>0.0098</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.0391</v>
+        <v>0.034</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0361</v>
+        <v>0.0401</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0391</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.0113</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0143</v>
+        <v>0.0197</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0269</v>
+        <v>0.0181</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0334</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0293</v>
+        <v>0.0375</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0297</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.025</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0438</v>
+        <v>0.0292</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.044</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0277</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.0119</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.008</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.0275</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0115</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0259</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0293</v>
+        <v>0.0388</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0252</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0134</v>
+        <v>0.0286</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0346</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0175</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.0184</v>
+        <v>0.0159</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0174</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0127</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0368</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.037</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0157</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0223</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0432</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0159</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0149</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.029</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.0064</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0186</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.0394</v>
+        <v>0.042</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0143</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.0318</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0111</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.0389</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0056</v>
+        <v>0.0244</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0237</v>
+        <v>0.0308</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0422</v>
+        <v>0.0409</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.008</v>
+        <v>0.0301</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.022</v>
+        <v>0.0212</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0209</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.032</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.0217</v>
+        <v>0.0112</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.0379</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0255</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0418</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0056</v>
+        <v>0.0164</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0282</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0056</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0203</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0262</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0431</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0186</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0405</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.0423</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.0423</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0102</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0053</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0295</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.0387</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0385</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0302</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0293</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0131</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0126</v>
+        <v>0.0107</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0407</v>
+        <v>0.026</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.0436</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0318</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0314</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0245</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.0338</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0222</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0394</v>
+        <v>0.0091</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.0438</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0366</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.015</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0279</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.024</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.0306</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0169</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0384</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0097</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.0324</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0383</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0185</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0183</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0195</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.018</v>
+        <v>0.0353</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0199</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0416</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0197</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0165</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0105</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0125</v>
+        <v>0.0117</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0448</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0054</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0262</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0383</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0272</v>
+        <v>0.0286</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0189</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0185</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0426</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0123</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.035</v>
+        <v>0.0284</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0367</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0153</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.0323</v>
+        <v>0.031</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0394</v>
+        <v>0.0294</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0319</v>
+        <v>0.0157</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0149</v>
+        <v>0.0358</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0375</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0346</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0409</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0101</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0206</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.0204</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0319</v>
+        <v>0.0311</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0444</v>
+        <v>0.0337</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0176</v>
+        <v>0.0341</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0065</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0431</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0327</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0375</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.0075</v>
+        <v>0.025</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0434</v>
+        <v>0.0196</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0279</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0406</v>
+        <v>0.0091</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.0408</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0442</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0419</v>
+        <v>0.0395</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0298</v>
+        <v>0.0294</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0161</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0371</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0401</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.041</v>
+        <v>0.0288</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.0202</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0181</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.039</v>
+        <v>0.0201</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0276</v>
+        <v>0.0124</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0356</v>
+        <v>0.0428</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.02</v>
+        <v>0.038</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0236</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.0065</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0266</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0386</v>
+        <v>0.0267</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0354</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0136</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.015</v>
+        <v>0.0313</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.0207</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0141</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0078</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0188</v>
+        <v>0.0328</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0372</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0227</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0374</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0365</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0149</v>
+        <v>0.0051</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0233</v>
+        <v>0.0277</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0299</v>
+        <v>0.0172</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0377</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0342</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.0336</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0274</v>
+        <v>0.0435</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.0238</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.0061</v>
+        <v>0.024</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0116</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0381</v>
+        <v>0.0123</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0137</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.032</v>
+        <v>0.0279</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0415</v>
+        <v>0.0437</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0208</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0189</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0155</v>
+        <v>0.0398</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.038</v>
+        <v>0.0367</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0393</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0279</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0449</v>
+        <v>0.0194</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0349</v>
+        <v>0.0428</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0264</v>
+        <v>0.0253</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0382</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0287</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0252</v>
+        <v>0.0164</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.0382</v>
+        <v>0.026</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.0254</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0169</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.036</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0334</v>
+        <v>0.0439</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0339</v>
+        <v>0.0247</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0209</v>
+        <v>0.0076</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0197</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.0239</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0411</v>
+        <v>0.0256</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0404</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0339</v>
+        <v>0.0268</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0285</v>
+        <v>0.0313</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0083</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0439</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0216</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0435</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0246</v>
+        <v>0.0431</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0379</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.033</v>
+        <v>0.0194</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.0145</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0242</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0376</v>
+        <v>0.0362</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0134</v>
+        <v>0.0435</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0363</v>
+        <v>0.0171</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0163</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0437</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.0257</v>
+        <v>0.043</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0288</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.0191</v>
+        <v>0.042</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0347</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0352</v>
+        <v>0.0326</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0349</v>
+        <v>0.0068</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0394</v>
+        <v>0.0145</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.0117</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0285</v>
+        <v>0.0345</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.0256</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0148</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0204</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0276</v>
+        <v>0.0272</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0139</v>
+        <v>0.0282</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0441</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0428</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0402</v>
+        <v>0.0368</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0308</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0334</v>
+        <v>0.0371</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0385</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.017</v>
+        <v>0.0424</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0331</v>
+        <v>0.0325</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.0198</v>
+        <v>0.031</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.042</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0307</v>
+        <v>0.0309</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>

--- a/reports/Unit_Validation_Test_Report.xlsx
+++ b/reports/Unit_Validation_Test_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0276</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0448</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0327</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0071</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0148</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0231</v>
+        <v>0.0396</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.0352</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.0419</v>
+        <v>0.0363</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0186</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.0061</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0225</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.007</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.0413</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0074</v>
+        <v>0.0353</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0414</v>
+        <v>0.0081</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0072</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.0392</v>
+        <v>0.0095</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.0175</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0429</v>
+        <v>0.0283</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0207</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0363</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0325</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0443</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0148</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0119</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.0154</v>
+        <v>0.0121</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.0396</v>
+        <v>0.0207</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0368</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0301</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.014</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0229</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0272</v>
+        <v>0.0311</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.0241</v>
+        <v>0.0264</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0399</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.0146</v>
+        <v>0.0115</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.0074</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0277</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0413</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.0069</v>
+        <v>0.0201</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0231</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0338</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0373</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0375</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.0224</v>
+        <v>0.0214</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.0133</v>
+        <v>0.0056</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.0234</v>
+        <v>0.0139</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0086</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.0222</v>
+        <v>0.0157</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0098</v>
+        <v>0.0321</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.034</v>
+        <v>0.0164</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0319</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.0391</v>
+        <v>0.0358</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.0113</v>
+        <v>0.028</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0383</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0058</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.0334</v>
+        <v>0.0287</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.011</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.0297</v>
+        <v>0.0205</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0341</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.0292</v>
+        <v>0.0248</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.044</v>
+        <v>0.0268</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0158</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0119</v>
+        <v>0.0242</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.008</v>
+        <v>0.0317</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.0275</v>
+        <v>0.0316</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0115</v>
+        <v>0.0076</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0259</v>
+        <v>0.0438</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.0179</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0252</v>
+        <v>0.0346</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.039</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0155</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.0175</v>
+        <v>0.0168</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0177</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.022</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.0174</v>
+        <v>0.0271</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0116</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0292</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.037</v>
+        <v>0.0401</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0307</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0052</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.0432</v>
+        <v>0.0286</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.0159</v>
+        <v>0.0332</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.0149</v>
+        <v>0.042</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.029</v>
+        <v>0.0222</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.0064</v>
+        <v>0.0217</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0072</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0385</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0143</v>
+        <v>0.0264</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0165</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.0111</v>
+        <v>0.0195</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.0389</v>
+        <v>0.0217</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.0244</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0442</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.018</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.0301</v>
+        <v>0.0439</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.0212</v>
+        <v>0.0097</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.0209</v>
+        <v>0.0189</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.032</v>
+        <v>0.0051</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.034</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0351</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.0255</v>
+        <v>0.0284</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.0418</v>
+        <v>0.0209</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0194</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0418</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.0056</v>
+        <v>0.0323</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.0203</v>
+        <v>0.0407</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0268</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0102</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0186</v>
+        <v>0.0173</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0426</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.0107</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.0378</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0125</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0102</v>
+        <v>0.0402</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0053</v>
+        <v>0.0374</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.0295</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0428</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.0387</v>
+        <v>0.0396</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0381</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0216</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.0302</v>
+        <v>0.01</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.0293</v>
+        <v>0.0268</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.0131</v>
+        <v>0.0241</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.0107</v>
+        <v>0.0127</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0109</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0443</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0318</v>
+        <v>0.0136</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.0314</v>
+        <v>0.0292</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0245</v>
+        <v>0.0156</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.0338</v>
+        <v>0.0191</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.0222</v>
+        <v>0.0207</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0314</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.0438</v>
+        <v>0.0419</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.0366</v>
+        <v>0.0435</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0166</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.038</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.0306</v>
+        <v>0.0248</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0163</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.0384</v>
+        <v>0.0118</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0097</v>
+        <v>0.0433</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0324</v>
+        <v>0.0212</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0291</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.0336</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.0183</v>
+        <v>0.0255</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.0195</v>
+        <v>0.0308</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.0167</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.016</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.0416</v>
+        <v>0.0183</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0295</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.0131</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.0105</v>
+        <v>0.0271</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.039</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0403</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.0448</v>
+        <v>0.018</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0122</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0139</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.042</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.0286</v>
+        <v>0.0289</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0392</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.0412</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0206</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0179</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.0284</v>
+        <v>0.0337</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.019</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.0153</v>
+        <v>0.0133</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.031</v>
+        <v>0.0171</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0314</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.0396</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0247</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.025</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0167</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.0346</v>
+        <v>0.0237</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0143</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.0101</v>
+        <v>0.0105</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.0206</v>
+        <v>0.0161</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0197</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.0311</v>
+        <v>0.0322</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.0337</v>
+        <v>0.0075</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.0341</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0316</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0245</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.0327</v>
+        <v>0.0137</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.0375</v>
+        <v>0.0358</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0431</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.0196</v>
+        <v>0.0321</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.02</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.0091</v>
+        <v>0.0175</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.021</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.0442</v>
+        <v>0.0287</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.0395</v>
+        <v>0.0142</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.0094</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.0161</v>
+        <v>0.0086</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.0371</v>
+        <v>0.0072</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.0401</v>
+        <v>0.0396</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.0167</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.0202</v>
+        <v>0.0271</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.0181</v>
+        <v>0.0276</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.0201</v>
+        <v>0.0336</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.0124</v>
+        <v>0.0191</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0408</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0303</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.038</v>
+        <v>0.007</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.0236</v>
+        <v>0.0424</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.0065</v>
+        <v>0.0398</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0207</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.0373</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.0354</v>
+        <v>0.0113</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.0136</v>
+        <v>0.0139</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0112</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.0333</v>
+        <v>0.0202</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.0207</v>
+        <v>0.0195</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0403</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.0078</v>
+        <v>0.0248</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.0328</v>
+        <v>0.0442</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.0372</v>
+        <v>0.0343</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.0227</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.0374</v>
+        <v>0.0445</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.033</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.0051</v>
+        <v>0.0438</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.0337</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.0172</v>
+        <v>0.025</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.0377</v>
+        <v>0.0055</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.0342</v>
+        <v>0.0105</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.0336</v>
+        <v>0.0081</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0202</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.0238</v>
+        <v>0.0311</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.024</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.0116</v>
+        <v>0.0191</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.0123</v>
+        <v>0.0263</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0128</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.0137</v>
+        <v>0.0401</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0397</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.038</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.0208</v>
+        <v>0.0259</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.025</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.0398</v>
+        <v>0.035</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.0367</v>
+        <v>0.0351</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.0393</v>
+        <v>0.0105</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.0279</v>
+        <v>0.0251</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0284</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0431</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.0253</v>
+        <v>0.0326</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.0382</v>
+        <v>0.0421</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.0287</v>
+        <v>0.0053</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.0164</v>
+        <v>0.0354</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.0223</v>
+        <v>0.0101</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.026</v>
+        <v>0.0417</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.0254</v>
+        <v>0.0115</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.0169</v>
+        <v>0.0346</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0214</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0177</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.0247</v>
+        <v>0.0303</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.0076</v>
+        <v>0.0352</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.0197</v>
+        <v>0.0249</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.0378</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0305</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.0404</v>
+        <v>0.0242</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.0268</v>
+        <v>0.0287</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.0313</v>
+        <v>0.0117</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.007</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.0439</v>
+        <v>0.0391</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.0216</v>
+        <v>0.0051</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.035</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.0431</v>
+        <v>0.0345</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.0194</v>
+        <v>0.0282</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0184</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.039</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.0362</v>
+        <v>0.0244</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0436</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.0199</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.0163</v>
+        <v>0.0216</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0213</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0125</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.0288</v>
+        <v>0.0133</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0141</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.027</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.0326</v>
+        <v>0.0127</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.0068</v>
+        <v>0.0127</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0166</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.0117</v>
+        <v>0.0246</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.0345</v>
+        <v>0.0146</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.0256</v>
+        <v>0.0374</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.0148</v>
+        <v>0.0317</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.0204</v>
+        <v>0.0175</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.0272</v>
+        <v>0.0223</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.0282</v>
+        <v>0.0413</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.0441</v>
+        <v>0.0379</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.0428</v>
+        <v>0.0221</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.0368</v>
+        <v>0.0359</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.0308</v>
+        <v>0.0301</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.0371</v>
+        <v>0.0164</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.0094</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0189</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.0325</v>
+        <v>0.0238</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.031</v>
+        <v>0.0065</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0217</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.0309</v>
+        <v>0.0325</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
